--- a/Dataset/1_label/UP_UP_V2_10 divisions_per_second.xlsx
+++ b/Dataset/1_label/UP_UP_V2_10 divisions_per_second.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3438,6 +3438,60 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>UP_UP_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C168" t="n">
+        <v>3</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>UP_UP_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>35200</v>
+      </c>
+      <c r="C169" t="n">
+        <v>3</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>UP_UP_V2_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>35400</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>steady</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
